--- a/1차 개발 설계서/07 결정 및 자료 차이.xlsx
+++ b/1차 개발 설계서/07 결정 및 자료 차이.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자료목록" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'자료차이와반영'!$A$1:$F$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'자료차이와반영'!$A$1:$F$31</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'자료차이와반영'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'기술결정'!$A$1:$F$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'기술결정'!$1:$1</definedName>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -695,22 +695,22 @@
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>초대 관리</t>
+          <t>초대 권한</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>XLSX API·초대관리</t>
+          <t>2026-10-24 사용자 요청</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>단일 코드 교체·기간 선택</t>
+          <t>방장만 조회·발급·공유·취소</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>초대별168시간·기존 발급 유지·개별취소</t>
+          <t>모든 현재 참여자가 같은 모임의 초대 조회·발급·공유·복사·개별 취소</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -720,462 +720,462 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>invite 독립 테이블·UI23</t>
+          <t>UI05·UI23·권한표·3개 API member 권한·참여 종료 재검증</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>비로그인 미리보기</t>
+          <t>초대 관리</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>XLSX 화면흐름·권한</t>
+          <t>XLSX API·초대관리</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>대표사진·일부 일정 둘러보기</t>
+          <t>단일 코드 교체·기간 선택</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>모임명·일정요약만</t>
+          <t>초대별168시간·기존 발급 유지·개별취소</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>권한절·F05</t>
+          <t>F05</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>비공개 최소 DTO·UI24</t>
+          <t>invite 독립 테이블·UI23</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>참여 확정</t>
+          <t>비로그인 미리보기</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>XLSX 화면흐름 F29</t>
+          <t>XLSX 화면흐름·권한</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>로그인 뒤 자동 참여</t>
+          <t>대표사진·일부 일정 둘러보기</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>로그인/가입 후 참여하기로 확정</t>
+          <t>모임명·일정요약만</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>F05</t>
+          <t>권한절·F05</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>pendingInvite 보존 후 재확인</t>
+          <t>비공개 최소 DTO·UI24</t>
         </is>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>프로필</t>
+          <t>참여 확정</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>PDF p10·XLSX 프로필</t>
+          <t>XLSX 화면흐름 F29</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>사진·닉네임·합류율</t>
+          <t>로그인 뒤 자동 참여</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>표시명만·사진편집 없음</t>
+          <t>로그인/가입 후 참여하기로 확정</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>F05</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>UI28에서 표시명만</t>
+          <t>pendingInvite 보존 후 재확인</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>과거 날짜</t>
+          <t>프로필</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>XLSX 선택근거 T11</t>
+          <t>PDF p10·XLSX 프로필</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>minDate=오늘</t>
+          <t>사진·닉네임·합류율</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>과거 일정 허용·기한 지난 업로드 불가</t>
+          <t>표시명만·사진편집 없음</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>F07·F21</t>
+          <t>F02</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>생성 검증 분리</t>
+          <t>UI28에서 표시명만</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>촬영 길이</t>
+          <t>과거 날짜</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>PDF p8~9</t>
+          <t>XLSX 선택근거 T11</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>모임별5·10·15초</t>
+          <t>minDate=오늘</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>개인 촬영1~5초·기본3초</t>
+          <t>과거 일정 허용·기한 지난 업로드 불가</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>F12</t>
+          <t>F07·F21</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>UI15 정수 선택</t>
+          <t>생성 검증 분리</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>가져오기 길이</t>
+          <t>촬영 길이</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PDF p9</t>
+          <t>PDF p8~9</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>선택구간 자르기</t>
+          <t>모임별5·10·15초</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>가져오기60초·200MB, 자르기 없음</t>
+          <t>개인 촬영1~5초·기본3초</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>F13</t>
+          <t>F12</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>초과 영상 재선택 안내</t>
+          <t>UI15 정수 선택</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>장소별 개수</t>
+          <t>가져오기 길이</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>PDF p7·APK</t>
+          <t>PDF p9</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>슬롯/업로드 현황 중심</t>
+          <t>선택구간 자르기</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>v1은 제한 없음 → 2026-10-20 회의로 작성자별 방문당 사진5·영상2</t>
+          <t>가져오기60초·200MB, 자르기 없음</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>F14·P11</t>
+          <t>F13</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>남은 개수 표시·서버 파일별 거부</t>
+          <t>초과 영상 재선택 안내</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>소통 기능</t>
+          <t>장소별 개수</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>PDF p7</t>
+          <t>PDF p7·APK</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>실시간 댓글</t>
+          <t>슬롯/업로드 현황 중심</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>댓글·좋아요·친구·공개피드 제외</t>
+          <t>v1은 제한 없음 → 2026-10-20 회의로 작성자별 방문당 사진5·영상2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>개발범위</t>
+          <t>F14·P11</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>UI와 API에서 제거</t>
+          <t>남은 개수 표시·서버 파일별 거부</t>
         </is>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>삭제와 종료</t>
+          <t>소통 기능</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>XLSX 데이터정책·화면흐름</t>
+          <t>PDF p7</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>방장 여행 삭제·연쇄 삭제</t>
+          <t>실시간 댓글</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>빈 일정만 삭제, 마지막 방장만 모임종료·타인파일보존</t>
+          <t>댓글·좋아요·친구·공개피드 제외</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>F11·F23</t>
+          <t>개발범위</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>FK cascade 금지·UI27</t>
+          <t>UI와 API에서 제거</t>
         </is>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>로그아웃</t>
+          <t>삭제와 종료</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>XLSX 화면흐름 F05</t>
+          <t>XLSX 데이터정책·화면흐름</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>즉시 세션 해제</t>
+          <t>방장 여행 삭제·연쇄 삭제</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>미완료 업로드 확인·중단 선택</t>
+          <t>빈 일정만 삭제, 마지막 방장만 모임종료·타인파일보존</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>F28</t>
+          <t>F11·F23</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>UI28 확인 흐름</t>
+          <t>FK cascade 금지·UI27</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>지도·기록 범위</t>
+          <t>로그아웃</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>XLSX 문서정보</t>
+          <t>XLSX 화면흐름 F05</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>지도·업로드는 다음 단계</t>
+          <t>즉시 세션 해제</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>장소 검색·촬영·업로드·공동감상 1차 포함</t>
+          <t>미완료 업로드 확인·중단 선택</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>F09~F20</t>
+          <t>F28</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>1차에 설계 추가</t>
+          <t>UI28 확인 흐름</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>영상 제작·결제</t>
+          <t>지도·기록 범위</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>PDF p11~12·APK 실험</t>
+          <t>XLSX 문서정보</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>영상합성·분할·AI 아이디어</t>
+          <t>지도·업로드는 다음 단계</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>영상 제작/편집·결제·보관연장 후속</t>
+          <t>장소 검색·촬영·업로드·공동감상 1차 포함</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7절</t>
+          <t>F09~F20</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>개발/검수 범위 제외</t>
+          <t>1차에 설계 추가</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>보관</t>
+          <t>영상 제작·결제</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>PDF 검토문제·구자료</t>
+          <t>PDF p11~12·APK 실험</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>보관 미정/여행 삭제 종속</t>
+          <t>영상합성·분할·AI 아이디어</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>첫 완료 때 종료일+3개월 고정</t>
+          <t>영상 제작/편집·결제·보관연장 후속</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>F21</t>
+          <t>7절</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>서버 만료와 정리 분리</t>
+          <t>개발/검수 범위 제외</t>
         </is>
       </c>
     </row>
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>반복 일정</t>
+          <t>보관</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 회의</t>
+          <t>PDF 검토문제·구자료</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>v1: 일/주/월/년·간격·730회 맞춤 반복</t>
+          <t>보관 미정/여행 삭제 종속</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>반복 폐지, 기간(시작~종료 날짜) 일정을 방장이 수동 추가</t>
+          <t>첫 완료 때 종료일+3개월 고정</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>F07·F08·F11</t>
+          <t>F21</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>UI07 제거·recurrence 테이블/API 제거·scheduleUpdate/Cancel</t>
+          <t>서버 만료와 정리 분리</t>
         </is>
       </c>
     </row>
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>일정 시각</t>
+          <t>반복 일정</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1185,29 +1185,29 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>v1: 종일/시간 지정(UI04 종일 토글)</t>
+          <t>v1: 일/주/월/년·간격·730회 맞춤 반복</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>일정은 날짜만, 시각은 장소 추가 시 방문별 입력·UI08 표시</t>
+          <t>반복 폐지, 기간(시작~종료 날짜) 일정을 방장이 수동 추가</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>F07·F09·F10</t>
+          <t>F07·F08·F11</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>UI04/06 종일 제거·visitCreate.plannedTime·schedules 시각 컬럼 제거</t>
+          <t>UI07 제거·recurrence 테이블/API 제거·scheduleUpdate/Cancel</t>
         </is>
       </c>
     </row>
     <row r="24" ht="34" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>초대 횟수</t>
+          <t>일정 시각</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1217,29 +1217,29 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>v1: 7일·횟수 무제한</t>
+          <t>v1: 종일/시간 지정(UI04 종일 토글)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7일 + 초대 확인 50회 소진</t>
+          <t>일정은 날짜만, 시각은 장소 추가 시 방문별 입력·UI08 표시</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>F05</t>
+          <t>F07·F09·F10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>invitations.use_count/max_uses·INVITE_EXHAUSTED·UI23/24</t>
+          <t>UI04/06 종일 제거·visitCreate.plannedTime·schedules 시각 컬럼 제거</t>
         </is>
       </c>
     </row>
     <row r="25" ht="34" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>외부 공유</t>
+          <t>초대 횟수</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1249,29 +1249,29 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>v1: 휴대폰 저장 + OS 공유창</t>
+          <t>v1: 7일·횟수 무제한</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>휴대폰 저장만. 초대 메시지 공유는 유지</t>
+          <t>7일 + 초대 확인 50회 소진</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>F19·F20·F23</t>
+          <t>F05</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>UI21 공유 제거·export purpose=save</t>
+          <t>invitations.use_count/max_uses·INVITE_EXHAUSTED·UI23/24</t>
         </is>
       </c>
     </row>
     <row r="26" ht="34" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>장소별 업로드 수</t>
+          <t>외부 공유</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1281,29 +1281,29 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>v1: 제한 없음</t>
+          <t>v1: 휴대폰 저장 + OS 공유창</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>작성자별 방문당 사진5·영상2, 미지정은 작성자×일정×기록일</t>
+          <t>휴대폰 저장만. 초대 메시지 공유는 유지</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>F14·F17·P11</t>
+          <t>F19·F20·F23</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>upload_tasks/media 트리거 MEDIA_LIMIT·UI13/16 남은 개수</t>
+          <t>UI21 공유 제거·export purpose=save</t>
         </is>
       </c>
     </row>
     <row r="27" ht="34" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>일차별 장소 수</t>
+          <t>장소별 업로드 수</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1318,24 +1318,24 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>일정×방문일 방문 최대 15개</t>
+          <t>작성자별 방문당 사진5·영상2, 미지정은 작성자×일정×기록일</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>F09·P12</t>
+          <t>F14·F17·P11</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>visits 트리거 VISIT_LIMIT·UI08/10/11</t>
+          <t>upload_tasks/media 트리거 MEDIA_LIMIT·UI13/16 남은 개수</t>
         </is>
       </c>
     </row>
     <row r="28" ht="34" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>선택 화면</t>
+          <t>일차별 장소 수</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1345,29 +1345,29 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>v1: UI16 업로드 확인 + UI19 다중 선택</t>
+          <t>v1: 제한 없음</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>하나의 선택 화면으로 통합</t>
+          <t>일정×방문일 방문 최대 15개</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>F14·F17·F18·F19</t>
+          <t>F09·P12</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>UI16 통합·UI19 번호 폐지</t>
+          <t>visits 트리거 VISIT_LIMIT·UI08/10/11</t>
         </is>
       </c>
     </row>
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>기록 보기 방식</t>
+          <t>선택 화면</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1377,59 +1377,91 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>v1: 제출 묶음 완료순 고정</t>
+          <t>v1: UI16 업로드 확인 + UI19 다중 선택</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>시간순(촬영 시각)·사람별 묶음</t>
+          <t>하나의 선택 화면으로 통합</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>F16</t>
+          <t>F14·F17·F18·F19</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>mediaList view/order·UI09/13</t>
+          <t>UI16 통합·UI19 번호 폐지</t>
         </is>
       </c>
     </row>
     <row r="30" ht="34" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>기록 보기 방식</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 회의</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>v1: 제출 묶음 완료순 고정</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>시간순(촬영 시각)·사람별 묶음</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>F16</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>mediaList view/order·UI09/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
           <t>길게 눌러 저장</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>2026-10-20 회의</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>v1: 선택 버튼 중심</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>길게 누르기 → 다중 선택 → 휴대폰 저장</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>F16·F19</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>UI09/13/16 선택 모드</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F30"/>
+  <autoFilter ref="A1:F31"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
@@ -2426,7 +2458,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>설계 자료/프로젝트 소개.pdf</t>
+          <t>참고 자료/프로젝트 소개.pdf</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -2448,7 +2480,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>설계 자료/화면 명세 데이터.xlsx</t>
+          <t>참고 자료/화면 명세 데이터.xlsx</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2470,7 +2502,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>기능 명세서 자료/ReelSpot-Demo.apk</t>
+          <t>근거/APK/실행검토.json (과거 APK 관찰; 원본 바이너리 제거)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2492,7 +2524,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>기능 명세서 자료/artifacts/research/2026-10-17_1차_세부기능_결정근거.md</t>
+          <t>../기능 명세서/참고 자료/2026-10-17_1차_세부기능_결정근거.md</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2514,7 +2546,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>10월_20일_회의.md</t>
+          <t>../회의록/10월_20일_회의.md</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2536,7 +2568,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>설계_피드백_검토_및_대응방향.md</t>
+          <t>../회의록/10월_20일_회의_반영_내역.md</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">

--- a/1차 개발 설계서/07 결정 및 자료 차이.xlsx
+++ b/1차 개발 설계서/07 결정 및 자료 차이.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자료목록" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'자료차이와반영'!$A$1:$F$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'자료차이와반영'!$A$1:$F$38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'자료차이와반영'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'기술결정'!$A$1:$F$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'기술결정'!$1:$1</definedName>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1460,8 +1460,232 @@
         </is>
       </c>
     </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>A01 날짜 추가</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>c19f34c DatePickSheet/demoStore</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>비연속 날짜 다중 선택·30개</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>방장만 연속366일·버전/영향 확인</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>F07 F08 F21</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>회의 10/30 A01 결정 전 기존 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>A02 진입</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>c19f34c S01/S02/S04</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>날짜·방문을 순차 경유</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>전체 기본·미지정/기간 밖 직접 경로</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>F06 F16</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>UI08 날짜 카드를 필터로 연결</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>A03 정렬</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>c19f34c PlaceRecords</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>업로드 최신순·보기 초기화</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>촬영 시각 오름차순·기기 기억</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>F16</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>아이콘/선택 UI만 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>A04 대표 사진</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>c19f34c covers[itinerary.id]</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>일정별 커버</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>모임별 커버·방장만</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>UI25 연결·일정별 데이터 보류</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>A05 프로필</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>c19f34c MyPage/Account</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>사진 편집·복원</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>표시명·기본 아이콘</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>F02 F28</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>UI36/37 구성 반영·사진 보류</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>A09 저장</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>c19f34c downloadBridge</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>handled 응답·연결 안내</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>120개·파일별 결과·실패 재시도</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>F16 F19</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>UI16→UI21 계약 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>A13 출시 정합성</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>약관13 개정안 vs 종전 명세</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>동의·GPS·계정 삭제 규칙 차이</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>별도 개정 확정 필요</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>F02 F20 F24</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>일반 사용자 출시 전 해결·이번 UI 검증으로 대체 불가</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F31"/>
+  <autoFilter ref="A1:F38"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
